--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,11 +385,6 @@
           <t>valor_previo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>seleccionado</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -414,9 +409,6 @@
       <c r="F2">
         <v>9.369999999999999</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,9 +433,6 @@
       <c r="F3">
         <v>11.85</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,9 +457,6 @@
       <c r="F4">
         <v>12.76</v>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,9 +481,6 @@
       <c r="F5">
         <v>10.83</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,9 +505,6 @@
       <c r="F6">
         <v>11.62</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,9 +529,6 @@
       <c r="F7">
         <v>12.4</v>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,9 +553,6 @@
       <c r="F8">
         <v>15.21</v>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -603,9 +577,6 @@
       <c r="F9">
         <v>17.9</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,9 +601,6 @@
       <c r="F10">
         <v>18.36</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -657,9 +625,6 @@
       <c r="F11">
         <v>17.08</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -684,9 +649,6 @@
       <c r="F12">
         <v>17.52</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -711,9 +673,6 @@
       <c r="F13">
         <v>19.91</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -738,9 +697,6 @@
       <c r="F14">
         <v>19.73</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -765,9 +721,6 @@
       <c r="F15">
         <v>21.48</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -792,9 +745,6 @@
       <c r="F16">
         <v>22.36</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -818,9 +768,6 @@
       </c>
       <c r="F17">
         <v>21.21</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,20 +367,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>anio_actual</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>valor_actual</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>anio_previo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>valor_previo</t>
         </is>
@@ -398,15 +403,18 @@
         </is>
       </c>
       <c r="C2">
-        <v>2020</v>
+        <v>2</v>
       </c>
       <c r="D2">
+        <v>2020</v>
+      </c>
+      <c r="E2">
         <v>9.16</v>
       </c>
-      <c r="E2">
-        <v>2019</v>
-      </c>
       <c r="F2">
+        <v>2019</v>
+      </c>
+      <c r="G2">
         <v>9.369999999999999</v>
       </c>
     </row>
@@ -422,15 +430,18 @@
         </is>
       </c>
       <c r="C3">
-        <v>2020</v>
+        <v>3</v>
       </c>
       <c r="D3">
+        <v>2020</v>
+      </c>
+      <c r="E3">
         <v>10.35</v>
       </c>
-      <c r="E3">
-        <v>2019</v>
-      </c>
       <c r="F3">
+        <v>2019</v>
+      </c>
+      <c r="G3">
         <v>11.85</v>
       </c>
     </row>
@@ -446,15 +457,18 @@
         </is>
       </c>
       <c r="C4">
-        <v>2020</v>
+        <v>11</v>
       </c>
       <c r="D4">
+        <v>2020</v>
+      </c>
+      <c r="E4">
         <v>10.86</v>
       </c>
-      <c r="E4">
-        <v>2019</v>
-      </c>
       <c r="F4">
+        <v>2019</v>
+      </c>
+      <c r="G4">
         <v>12.76</v>
       </c>
     </row>
@@ -466,19 +480,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Magallanes y la Antártica Chilena</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="C5">
-        <v>2020</v>
+        <v>12</v>
       </c>
       <c r="D5">
+        <v>2020</v>
+      </c>
+      <c r="E5">
         <v>11.68</v>
       </c>
-      <c r="E5">
-        <v>2019</v>
-      </c>
       <c r="F5">
+        <v>2019</v>
+      </c>
+      <c r="G5">
         <v>10.83</v>
       </c>
     </row>
@@ -494,15 +511,18 @@
         </is>
       </c>
       <c r="C6">
-        <v>2020</v>
+        <v>13</v>
       </c>
       <c r="D6">
+        <v>2020</v>
+      </c>
+      <c r="E6">
         <v>12.33</v>
       </c>
-      <c r="E6">
-        <v>2019</v>
-      </c>
       <c r="F6">
+        <v>2019</v>
+      </c>
+      <c r="G6">
         <v>11.62</v>
       </c>
     </row>
@@ -518,15 +538,18 @@
         </is>
       </c>
       <c r="C7">
-        <v>2020</v>
+        <v>1</v>
       </c>
       <c r="D7">
+        <v>2020</v>
+      </c>
+      <c r="E7">
         <v>12.71</v>
       </c>
-      <c r="E7">
-        <v>2019</v>
-      </c>
       <c r="F7">
+        <v>2019</v>
+      </c>
+      <c r="G7">
         <v>12.4</v>
       </c>
     </row>
@@ -542,15 +565,18 @@
         </is>
       </c>
       <c r="C8">
-        <v>2020</v>
+        <v>10</v>
       </c>
       <c r="D8">
+        <v>2020</v>
+      </c>
+      <c r="E8">
         <v>13.6</v>
       </c>
-      <c r="E8">
-        <v>2019</v>
-      </c>
       <c r="F8">
+        <v>2019</v>
+      </c>
+      <c r="G8">
         <v>15.21</v>
       </c>
     </row>
@@ -566,15 +592,18 @@
         </is>
       </c>
       <c r="C9">
-        <v>2020</v>
+        <v>8</v>
       </c>
       <c r="D9">
+        <v>2020</v>
+      </c>
+      <c r="E9">
         <v>13.75</v>
       </c>
-      <c r="E9">
-        <v>2019</v>
-      </c>
       <c r="F9">
+        <v>2019</v>
+      </c>
+      <c r="G9">
         <v>17.9</v>
       </c>
     </row>
@@ -590,15 +619,18 @@
         </is>
       </c>
       <c r="C10">
-        <v>2020</v>
+        <v>14</v>
       </c>
       <c r="D10">
+        <v>2020</v>
+      </c>
+      <c r="E10">
         <v>14.69</v>
       </c>
-      <c r="E10">
-        <v>2019</v>
-      </c>
       <c r="F10">
+        <v>2019</v>
+      </c>
+      <c r="G10">
         <v>18.36</v>
       </c>
     </row>
@@ -614,15 +646,18 @@
         </is>
       </c>
       <c r="C11">
-        <v>2020</v>
+        <v>4</v>
       </c>
       <c r="D11">
+        <v>2020</v>
+      </c>
+      <c r="E11">
         <v>14.9</v>
       </c>
-      <c r="E11">
-        <v>2019</v>
-      </c>
       <c r="F11">
+        <v>2019</v>
+      </c>
+      <c r="G11">
         <v>17.08</v>
       </c>
     </row>
@@ -638,15 +673,18 @@
         </is>
       </c>
       <c r="C12">
-        <v>2020</v>
+        <v>5</v>
       </c>
       <c r="D12">
+        <v>2020</v>
+      </c>
+      <c r="E12">
         <v>15.79</v>
       </c>
-      <c r="E12">
-        <v>2019</v>
-      </c>
       <c r="F12">
+        <v>2019</v>
+      </c>
+      <c r="G12">
         <v>17.52</v>
       </c>
     </row>
@@ -658,19 +696,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="C13">
-        <v>2020</v>
+        <v>15</v>
       </c>
       <c r="D13">
+        <v>2020</v>
+      </c>
+      <c r="E13">
         <v>16.25</v>
       </c>
-      <c r="E13">
-        <v>2019</v>
-      </c>
       <c r="F13">
+        <v>2019</v>
+      </c>
+      <c r="G13">
         <v>19.91</v>
       </c>
     </row>
@@ -682,19 +723,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="C14">
-        <v>2020</v>
+        <v>9</v>
       </c>
       <c r="D14">
+        <v>2020</v>
+      </c>
+      <c r="E14">
         <v>17.81</v>
       </c>
-      <c r="E14">
-        <v>2019</v>
-      </c>
       <c r="F14">
+        <v>2019</v>
+      </c>
+      <c r="G14">
         <v>19.73</v>
       </c>
     </row>
@@ -710,15 +754,18 @@
         </is>
       </c>
       <c r="C15">
-        <v>2020</v>
+        <v>16</v>
       </c>
       <c r="D15">
+        <v>2020</v>
+      </c>
+      <c r="E15">
         <v>18.21</v>
       </c>
-      <c r="E15">
-        <v>2019</v>
-      </c>
       <c r="F15">
+        <v>2019</v>
+      </c>
+      <c r="G15">
         <v>21.48</v>
       </c>
     </row>
@@ -734,15 +781,18 @@
         </is>
       </c>
       <c r="C16">
-        <v>2020</v>
+        <v>7</v>
       </c>
       <c r="D16">
+        <v>2020</v>
+      </c>
+      <c r="E16">
         <v>18.27</v>
       </c>
-      <c r="E16">
-        <v>2019</v>
-      </c>
       <c r="F16">
+        <v>2019</v>
+      </c>
+      <c r="G16">
         <v>22.36</v>
       </c>
     </row>
@@ -758,15 +808,18 @@
         </is>
       </c>
       <c r="C17">
-        <v>2020</v>
+        <v>6</v>
       </c>
       <c r="D17">
+        <v>2020</v>
+      </c>
+      <c r="E17">
         <v>18.3</v>
       </c>
-      <c r="E17">
-        <v>2019</v>
-      </c>
       <c r="F17">
+        <v>2019</v>
+      </c>
+      <c r="G17">
         <v>21.21</v>
       </c>
     </row>

--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="C13">

--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -1,46 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$17</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t xml:space="preserve">indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">region_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anio_actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anio_previo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_previo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I_perINGR_MEDIAN_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 20:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +169,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +249,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +274,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +305,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,480 +481,484 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>indicador</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>region_code</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>anio_actual</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>valor_actual</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>anio_previo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>valor_previo</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="C2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>2020</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>9.16</v>
       </c>
-      <c r="F2">
-        <v>2019</v>
-      </c>
-      <c r="G2">
-        <v>9.369999999999999</v>
+      <c r="F2" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>9.37</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="C3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>2020</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>10.35</v>
       </c>
-      <c r="F3">
-        <v>2019</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>11.85</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="C4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D4">
-        <v>2020</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>10.86</v>
       </c>
-      <c r="F4">
-        <v>2019</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>12.76</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="C5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D5">
-        <v>2020</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>11.68</v>
       </c>
-      <c r="F5">
-        <v>2019</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>10.83</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="C6">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D6">
-        <v>2020</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>12.33</v>
       </c>
-      <c r="F6">
-        <v>2019</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>11.62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="C7">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7">
-        <v>2020</v>
-      </c>
-      <c r="E7">
+      <c r="D7" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>12.71</v>
       </c>
-      <c r="F7">
-        <v>2019</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>12.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="C8">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D8">
-        <v>2020</v>
-      </c>
-      <c r="E8">
+      <c r="D8" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="F8">
-        <v>2019</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>15.21</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="C9">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D9">
-        <v>2020</v>
-      </c>
-      <c r="E9">
+      <c r="D9" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>13.75</v>
       </c>
-      <c r="F9">
-        <v>2019</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>17.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="C10">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D10">
-        <v>2020</v>
-      </c>
-      <c r="E10">
+      <c r="D10" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>14.69</v>
       </c>
-      <c r="F10">
-        <v>2019</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>18.36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="C11">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D11">
-        <v>2020</v>
-      </c>
-      <c r="E11">
+      <c r="D11" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="F11">
-        <v>2019</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>17.08</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="C12">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D12">
-        <v>2020</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>15.79</v>
       </c>
-      <c r="F12">
-        <v>2019</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>17.52</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="C13">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D13">
-        <v>2020</v>
-      </c>
-      <c r="E13">
+      <c r="D13" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>16.25</v>
       </c>
-      <c r="F13">
-        <v>2019</v>
-      </c>
-      <c r="G13">
+      <c r="F13" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>19.91</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>La Araucanía</t>
-        </is>
-      </c>
-      <c r="C14">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D14">
-        <v>2020</v>
-      </c>
-      <c r="E14">
+      <c r="D14" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>17.81</v>
       </c>
-      <c r="F14">
-        <v>2019</v>
-      </c>
-      <c r="G14">
+      <c r="F14" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>19.73</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="C15">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D15">
-        <v>2020</v>
-      </c>
-      <c r="E15">
+      <c r="D15" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>18.21</v>
       </c>
-      <c r="F15">
-        <v>2019</v>
-      </c>
-      <c r="G15">
+      <c r="F15" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>21.48</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>2020</v>
-      </c>
-      <c r="E16">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>18.27</v>
       </c>
-      <c r="F16">
-        <v>2019</v>
-      </c>
-      <c r="G16">
+      <c r="F16" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>22.36</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>I_perINGR_MEDIAN_a</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="C17">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D17">
-        <v>2020</v>
-      </c>
-      <c r="E17">
+      <c r="D17" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="F17">
-        <v>2019</v>
-      </c>
-      <c r="G17">
+      <c r="F17" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>21.21</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G17"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$18</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:56</t>
+    <t xml:space="preserve">2026-08-16 00:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -885,8 +885,27 @@
         <v>21.21</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>14.94</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
+++ b/output/graficos_regionales/plot_i_peringr_median_a_2020_aysen.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 00:01</t>
+    <t xml:space="preserve">2026-09-07 11:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
